--- a/data/gravel/Stinner Refugio Podium 2025.xlsx
+++ b/data/gravel/Stinner Refugio Podium 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9D4E5B-F486-054D-9EEF-94AFE899DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675C7AB-56DD-E143-8F26-994491BC3CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -333,6 +333,24 @@
   </si>
   <si>
     <t>a8:h33</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -689,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1404,10 +1422,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
       </c>
       <c r="C36">
         <v>62</v>
@@ -1430,10 +1448,10 @@
     </row>
     <row r="37" spans="1:8" ht="21">
       <c r="A37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>67</v>
+        <v>102</v>
+      </c>
+      <c r="B37" t="s">
+        <v>103</v>
       </c>
       <c r="C37" s="3">
         <v>65</v>
@@ -1456,7 +1474,10 @@
     </row>
     <row r="38" spans="1:8" ht="21">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>104</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -1465,222 +1486,243 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39">
-        <v>50</v>
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="B42">
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>38</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45">
-        <v>142</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46">
-        <v>100</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="B48">
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B49">
-        <v>27.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>95</v>
+        <v>44</v>
+      </c>
+      <c r="B52">
+        <v>27.2</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53">
-        <v>160</v>
+        <v>45</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B54">
-        <v>160</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>96</v>
+        <v>48</v>
+      </c>
+      <c r="B56">
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B57">
+        <v>160</v>
+      </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67">
-        <v>2895</v>
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68">
-        <v>5595</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B69" s="1"/>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71">
+        <v>5595</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>68</v>
       </c>
     </row>

--- a/data/gravel/Stinner Refugio Podium 2025.xlsx
+++ b/data/gravel/Stinner Refugio Podium 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675C7AB-56DD-E143-8F26-994491BC3CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E6684-79AC-2C49-A4B9-DD928C0BBAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://www.stinnerframeworks.com/cdn/shop/files/MG_1814_360x.jpg?v=1743282243</t>
   </si>
 </sst>
 </file>
@@ -753,6 +756,11 @@
         <v>98</v>
       </c>
     </row>
+    <row r="6" spans="1:8">
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Stinner Refugio Podium 2025.xlsx
+++ b/data/gravel/Stinner Refugio Podium 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E6684-79AC-2C49-A4B9-DD928C0BBAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69798778-71D9-934B-89D3-1491CA3AB89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -239,9 +239,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>Wheelbase</t>
   </si>
   <si>
@@ -354,6 +351,15 @@
   </si>
   <si>
     <t>https://www.stinnerframeworks.com/cdn/shop/files/MG_1814_360x.jpg?v=1743282243</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Santa Barbara, California, USA</t>
   </si>
 </sst>
 </file>
@@ -710,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -721,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -729,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -753,12 +759,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -766,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21">
@@ -774,25 +780,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" t="s">
         <v>76</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>77</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>78</v>
-      </c>
-      <c r="H8" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21">
@@ -800,7 +806,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3">
         <v>545</v>
@@ -826,7 +832,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="3">
         <v>387</v>
@@ -852,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3">
         <v>540</v>
@@ -878,7 +884,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3">
         <v>97</v>
@@ -904,7 +910,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3">
         <v>71.25</v>
@@ -927,10 +933,10 @@
     </row>
     <row r="14" spans="1:8" ht="21">
       <c r="A14" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3">
         <v>282</v>
@@ -956,7 +962,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="3">
         <v>82</v>
@@ -982,7 +988,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="3">
         <v>74.5</v>
@@ -1008,7 +1014,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17">
         <v>71</v>
@@ -1034,7 +1040,7 @@
         <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18">
         <v>603</v>
@@ -1060,7 +1066,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19">
         <v>438</v>
@@ -1086,7 +1092,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20">
         <v>1027</v>
@@ -1112,7 +1118,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21">
         <v>765</v>
@@ -1138,7 +1144,7 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22">
         <v>470</v>
@@ -1207,7 +1213,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1430,10 +1436,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
         <v>100</v>
-      </c>
-      <c r="B36" t="s">
-        <v>101</v>
       </c>
       <c r="C36">
         <v>62</v>
@@ -1456,10 +1462,10 @@
     </row>
     <row r="37" spans="1:8" ht="21">
       <c r="A37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
         <v>102</v>
-      </c>
-      <c r="B37" t="s">
-        <v>103</v>
       </c>
       <c r="C37" s="3">
         <v>65</v>
@@ -1482,10 +1488,10 @@
     </row>
     <row r="38" spans="1:8" ht="21">
       <c r="A38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s">
         <v>104</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -1497,7 +1503,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1568,7 +1574,7 @@
         <v>42</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1605,7 +1611,7 @@
         <v>47</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1634,7 +1640,7 @@
         <v>51</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1731,7 +1737,15 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>68</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Stinner Refugio Podium 2025.xlsx
+++ b/data/gravel/Stinner Refugio Podium 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69798778-71D9-934B-89D3-1491CA3AB89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F8830E-B67B-D64A-8839-A8EED158FF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -366,9 +366,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="4">
     <font>
       <sz val="14"/>
@@ -413,13 +410,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1322,116 +1318,104 @@
       <c r="A32" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="5">
-        <f>C34</f>
+      <c r="C32">
+        <f>C34*2.54</f>
         <v>157.47999999999999</v>
       </c>
-      <c r="D32" s="5">
-        <f>AVERAGE(D34,C35)</f>
-        <v>163.82999999999998</v>
-      </c>
-      <c r="E32" s="5">
-        <f t="shared" ref="E32:H32" si="0">AVERAGE(E34,D35)</f>
-        <v>168.91000000000003</v>
-      </c>
-      <c r="F32" s="5">
-        <f t="shared" si="0"/>
-        <v>173.99</v>
-      </c>
-      <c r="G32" s="5">
-        <f t="shared" si="0"/>
-        <v>179.07</v>
-      </c>
-      <c r="H32" s="5">
-        <f t="shared" si="0"/>
-        <v>184.15</v>
+      <c r="D32">
+        <f>D34*2.54</f>
+        <v>162.56</v>
+      </c>
+      <c r="E32">
+        <f>E34*2.54</f>
+        <v>167.64000000000001</v>
+      </c>
+      <c r="F32">
+        <f>F34*2.54</f>
+        <v>172.72</v>
+      </c>
+      <c r="G32">
+        <f>G34*2.54</f>
+        <v>177.8</v>
+      </c>
+      <c r="H32">
+        <f>H34*2.54</f>
+        <v>182.88</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="5">
-        <f>D32</f>
-        <v>163.82999999999998</v>
-      </c>
-      <c r="D33" s="5">
-        <f t="shared" ref="D33:G33" si="1">E32</f>
-        <v>168.91000000000003</v>
-      </c>
-      <c r="E33" s="5">
-        <f t="shared" si="1"/>
-        <v>173.99</v>
-      </c>
-      <c r="F33" s="5">
-        <f t="shared" si="1"/>
-        <v>179.07</v>
-      </c>
-      <c r="G33" s="5">
-        <f t="shared" si="1"/>
-        <v>184.15</v>
-      </c>
-      <c r="H33" s="5">
-        <f>H35</f>
+      <c r="C33">
+        <f>C35*2.54</f>
+        <v>165.1</v>
+      </c>
+      <c r="D33">
+        <f>D35*2.54</f>
+        <v>170.18</v>
+      </c>
+      <c r="E33">
+        <f>E35*2.54</f>
+        <v>175.26</v>
+      </c>
+      <c r="F33">
+        <f>F35*2.54</f>
+        <v>180.34</v>
+      </c>
+      <c r="G33">
+        <f>G35*2.54</f>
+        <v>185.42000000000002</v>
+      </c>
+      <c r="H33">
+        <f>H35*2.54</f>
         <v>193.04</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="C34">
-        <f t="shared" ref="C34:H35" si="2">C36*2.54</f>
-        <v>157.47999999999999</v>
+        <v>62</v>
       </c>
       <c r="D34">
-        <f t="shared" si="2"/>
-        <v>162.56</v>
+        <v>64</v>
       </c>
       <c r="E34">
-        <f t="shared" si="2"/>
-        <v>167.64000000000001</v>
+        <v>66</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
-        <v>172.72</v>
+        <v>68</v>
       </c>
       <c r="G34">
-        <f t="shared" si="2"/>
-        <v>177.8</v>
+        <v>70</v>
       </c>
       <c r="H34">
-        <f t="shared" si="2"/>
-        <v>182.88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="21">
       <c r="A35" t="s">
         <v>29</v>
       </c>
       <c r="B35" t="s">
         <v>30</v>
       </c>
-      <c r="C35">
-        <f t="shared" si="2"/>
-        <v>165.1</v>
-      </c>
-      <c r="D35">
-        <f t="shared" si="2"/>
-        <v>170.18</v>
-      </c>
-      <c r="E35">
-        <f t="shared" si="2"/>
-        <v>175.26</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="2"/>
-        <v>180.34</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="2"/>
-        <v>185.42000000000002</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="2"/>
-        <v>193.04</v>
+      <c r="C35" s="3">
+        <v>65</v>
+      </c>
+      <c r="D35" s="3">
+        <v>67</v>
+      </c>
+      <c r="E35" s="3">
+        <v>69</v>
+      </c>
+      <c r="F35" s="3">
+        <v>71</v>
+      </c>
+      <c r="G35" s="3">
+        <v>73</v>
+      </c>
+      <c r="H35" s="3">
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1441,49 +1425,13 @@
       <c r="B36" t="s">
         <v>100</v>
       </c>
-      <c r="C36">
-        <v>62</v>
-      </c>
-      <c r="D36">
-        <v>64</v>
-      </c>
-      <c r="E36">
-        <v>66</v>
-      </c>
-      <c r="F36">
-        <v>68</v>
-      </c>
-      <c r="G36">
-        <v>70</v>
-      </c>
-      <c r="H36">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="21">
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>101</v>
       </c>
       <c r="B37" t="s">
         <v>102</v>
-      </c>
-      <c r="C37" s="3">
-        <v>65</v>
-      </c>
-      <c r="D37" s="3">
-        <v>67</v>
-      </c>
-      <c r="E37" s="3">
-        <v>69</v>
-      </c>
-      <c r="F37" s="3">
-        <v>71</v>
-      </c>
-      <c r="G37" s="3">
-        <v>73</v>
-      </c>
-      <c r="H37" s="3">
-        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="21">

--- a/data/gravel/Stinner Refugio Podium 2025.xlsx
+++ b/data/gravel/Stinner Refugio Podium 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F8830E-B67B-D64A-8839-A8EED158FF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC723F82-954A-394A-AF36-3B7B9DCE29AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,9 +350,6 @@
     <t>rigid</t>
   </si>
   <si>
-    <t>https://www.stinnerframeworks.com/cdn/shop/files/MG_1814_360x.jpg?v=1743282243</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>Santa Barbara, California, USA</t>
+  </si>
+  <si>
+    <t>https://www.stinnerframeworks.com/cdn/shop/files/MG_1814_1300x.jpg?v=1743282243</t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1319,27 +1319,27 @@
         <v>27</v>
       </c>
       <c r="C32">
-        <f>C34*2.54</f>
+        <f t="shared" ref="C32:H33" si="0">C34*2.54</f>
         <v>157.47999999999999</v>
       </c>
       <c r="D32">
-        <f>D34*2.54</f>
+        <f t="shared" si="0"/>
         <v>162.56</v>
       </c>
       <c r="E32">
-        <f>E34*2.54</f>
+        <f t="shared" si="0"/>
         <v>167.64000000000001</v>
       </c>
       <c r="F32">
-        <f>F34*2.54</f>
+        <f t="shared" si="0"/>
         <v>172.72</v>
       </c>
       <c r="G32">
-        <f>G34*2.54</f>
+        <f t="shared" si="0"/>
         <v>177.8</v>
       </c>
       <c r="H32">
-        <f>H34*2.54</f>
+        <f t="shared" si="0"/>
         <v>182.88</v>
       </c>
     </row>
@@ -1348,27 +1348,27 @@
         <v>28</v>
       </c>
       <c r="C33">
-        <f>C35*2.54</f>
+        <f t="shared" si="0"/>
         <v>165.1</v>
       </c>
       <c r="D33">
-        <f>D35*2.54</f>
+        <f t="shared" si="0"/>
         <v>170.18</v>
       </c>
       <c r="E33">
-        <f>E35*2.54</f>
+        <f t="shared" si="0"/>
         <v>175.26</v>
       </c>
       <c r="F33">
-        <f>F35*2.54</f>
+        <f t="shared" si="0"/>
         <v>180.34</v>
       </c>
       <c r="G33">
-        <f>G35*2.54</f>
+        <f t="shared" si="0"/>
         <v>185.42000000000002</v>
       </c>
       <c r="H33">
-        <f>H35*2.54</f>
+        <f t="shared" si="0"/>
         <v>193.04</v>
       </c>
     </row>
@@ -1685,15 +1685,15 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>106</v>
+      </c>
+      <c r="B74" t="s">
         <v>107</v>
-      </c>
-      <c r="B74" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Stinner Refugio Podium 2025.xlsx
+++ b/data/gravel/Stinner Refugio Podium 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC723F82-954A-394A-AF36-3B7B9DCE29AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C107FC01-EA39-0548-93FA-4F015D3BED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>https://www.stinnerframeworks.com/cdn/shop/files/MG_1814_1300x.jpg?v=1743282243</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -712,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1519,128 +1537,117 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54">
-        <v>42</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B60">
+        <v>42</v>
+      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>67</v>
@@ -1648,51 +1655,92 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B70">
-        <v>2895</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71">
-        <v>5595</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77">
+        <v>5595</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="1"/>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>106</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>107</v>
       </c>
     </row>
